--- a/test-data/json-to-excel/excel/excel-output.xlsx
+++ b/test-data/json-to-excel/excel/excel-output.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -482,9 +482,72 @@
         <v>data_array 3-1, data_array3-2, data_array3-3</v>
       </c>
     </row>
+    <row r="5" xml:space="preserve">
+      <c r="A5" t="str">
+        <v>1 mal, zuletzt: 2025-02-27 12:13</v>
+      </c>
+      <c r="B5" t="str" xml:space="preserve">
+        <v xml:space="preserve">{"dateModified":"2025-02-27 12:12","who":"minime","what":"angelegt","details":"Neu angelegt."}
+{"dateModified":"2025-02-27 12:13","who":"user1","what":"geändert","details":"Das Dokument wurde geändert."}</v>
+      </c>
+      <c r="C5" t="str">
+        <v>1706d2d7-b6e8-4c5a-bbc1-12ed2172b238</v>
+      </c>
+      <c r="D5" t="str">
+        <v>data 1</v>
+      </c>
+      <c r="E5" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6" xml:space="preserve">
+      <c r="A6" t="str">
+        <v>1 mal, zuletzt: 2025-02-27 12:20</v>
+      </c>
+      <c r="B6" t="str" xml:space="preserve">
+        <v xml:space="preserve">{"dateModified":"2025-02-27 12:16","who":"minnime","what":"angelegt","details":"Neu angelegt."}
+{"dateModified":"2025-02-27 12:20","who":"user2","what":"geändert","details":"Das Dokument wurde geändert."}</v>
+      </c>
+      <c r="C6" t="str">
+        <v>83fae4be-7949-4180-a59b-21a736df89ab</v>
+      </c>
+      <c r="D6" t="str">
+        <v>data 2</v>
+      </c>
+      <c r="E6" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F6" t="str">
+        <v>data_array 2-1, data_array2-2</v>
+      </c>
+    </row>
+    <row r="7" xml:space="preserve">
+      <c r="A7" t="str">
+        <v>1 mal, zuletzt: 2025-02-27 12:14</v>
+      </c>
+      <c r="B7" t="str" xml:space="preserve">
+        <v xml:space="preserve">{"dateModified":"2025-02-27 12:13","who":"minnime","what":"angelegt","details":"Neu angelegt."}
+{"dateModified":"2025-02-27 12:14","who":"user3","what":"geändert","details":"Das Dokument wurde geändert."}</v>
+      </c>
+      <c r="C7" t="str">
+        <v>cde94ce9-a9c9-4834-8111-d4b66d0c53aa</v>
+      </c>
+      <c r="D7" t="str">
+        <v>data 3</v>
+      </c>
+      <c r="E7" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F7" t="str">
+        <v>data_array 3-1, data_array3-2, data_array3-3</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F7"/>
   </ignoredErrors>
 </worksheet>
 </file>